--- a/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-4.xlsx
+++ b/Doc_Test/Pruebas_Calidad/Pruebas_Unitarias/CEC-4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kevin\Desktop\App_Uv\AppAcompanhamientoUV\Doc_Test\Pruebas_Calidad\Pruebas_Unitarias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA8FD44-6FC8-47CC-A858-9DFEE41FC5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4D94BE-FE11-42B1-90FC-89A9DCF8680C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2FFDA8E8-6428-4D51-9D6D-F314F8731DBF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -240,6 +240,21 @@
   iat: 1752172809,
   exp: 1752518409
 }</t>
+  </si>
+  <si>
+    <t>CP-5</t>
+  </si>
+  <si>
+    <t>CP-5.1</t>
+  </si>
+  <si>
+    <t>CP-5.2</t>
+  </si>
+  <si>
+    <t>CP-5.3</t>
+  </si>
+  <si>
+    <t>Ingresar un correo válido</t>
   </si>
 </sst>
 </file>
@@ -427,10 +442,37 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -438,33 +480,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -822,135 +837,135 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" spans="2:11" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="20">
         <v>45848</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="2:11" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
     </row>
     <row r="10" spans="2:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="13"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="6" t="s">
         <v>6</v>
       </c>
@@ -977,23 +992,23 @@
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="16"/>
+      <c r="B12" s="11"/>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
@@ -1012,16 +1027,16 @@
       <c r="H12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="14" t="s">
         <v>41</v>
       </c>
       <c r="K12" s="17"/>
     </row>
     <row r="13" spans="2:11" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="16"/>
+      <c r="B13" s="11"/>
       <c r="C13" s="9" t="s">
         <v>16</v>
       </c>
@@ -1040,35 +1055,35 @@
       <c r="H13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="18"/>
-      <c r="J13" s="21"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="16"/>
       <c r="K13" s="17"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="16"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="10" t="s">
         <v>34</v>
       </c>
       <c r="F15" s="8" t="s">
@@ -1080,16 +1095,16 @@
       <c r="H15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="14" t="s">
         <v>41</v>
       </c>
       <c r="K15" s="17"/>
     </row>
     <row r="16" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="16"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="9" t="s">
         <v>26</v>
       </c>
@@ -1108,12 +1123,12 @@
       <c r="H16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="18"/>
-      <c r="J16" s="22"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="15"/>
       <c r="K16" s="17"/>
     </row>
     <row r="17" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B17" s="16"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="9" t="s">
         <v>27</v>
       </c>
@@ -1132,35 +1147,35 @@
       <c r="H17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="21"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="16"/>
       <c r="K17" s="17"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="16"/>
+      <c r="B19" s="11"/>
       <c r="C19" s="7" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="10" t="s">
         <v>50</v>
       </c>
       <c r="F19" s="8" t="s">
@@ -1172,16 +1187,16 @@
       <c r="H19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="I19" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J19" s="20" t="s">
+      <c r="J19" s="14" t="s">
         <v>41</v>
       </c>
       <c r="K19" s="17"/>
     </row>
     <row r="20" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="16"/>
+      <c r="B20" s="11"/>
       <c r="C20" s="7" t="s">
         <v>53</v>
       </c>
@@ -1200,12 +1215,12 @@
       <c r="H20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="18"/>
-      <c r="J20" s="22"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="15"/>
       <c r="K20" s="17"/>
     </row>
     <row r="21" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B21" s="16"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="7" t="s">
         <v>54</v>
       </c>
@@ -1224,35 +1239,35 @@
       <c r="H21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="18"/>
-      <c r="J21" s="21"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="16"/>
       <c r="K21" s="17"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B23" s="16"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="7" t="s">
         <v>60</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="F23" s="8" t="s">
@@ -1264,16 +1279,16 @@
       <c r="H23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="14" t="s">
         <v>41</v>
       </c>
       <c r="K23" s="17"/>
     </row>
     <row r="24" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="16"/>
+      <c r="B24" s="11"/>
       <c r="C24" s="7" t="s">
         <v>61</v>
       </c>
@@ -1292,12 +1307,12 @@
       <c r="H24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="22"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="15"/>
       <c r="K24" s="17"/>
     </row>
     <row r="25" spans="2:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B25" s="16"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="7" t="s">
         <v>62</v>
       </c>
@@ -1316,35 +1331,35 @@
       <c r="H25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="21"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="16"/>
       <c r="K25" s="17"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="14" t="s">
+      <c r="B26" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
     <row r="27" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B27" s="16"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>50</v>
       </c>
       <c r="F27" s="8" t="s">
@@ -1356,18 +1371,18 @@
       <c r="H27" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J27" s="20" t="s">
+      <c r="J27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="2:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="16"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>57</v>
@@ -1384,14 +1399,14 @@
       <c r="H28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="18"/>
-      <c r="J28" s="22"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="15"/>
       <c r="K28" s="17"/>
     </row>
     <row r="29" spans="2:11" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="B29" s="16"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>38</v>
@@ -1408,27 +1423,22 @@
       <c r="H29" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="I29" s="18"/>
-      <c r="J29" s="21"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="16"/>
       <c r="K29" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="C26:K26"/>
-    <mergeCell ref="I27:I29"/>
-    <mergeCell ref="J27:J29"/>
-    <mergeCell ref="K27:K29"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C22:K22"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="J23:J25"/>
-    <mergeCell ref="K23:K25"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C9:K9"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C6:K6"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="I15:I17"/>
@@ -1438,16 +1448,21 @@
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="J12:J13"/>
     <mergeCell ref="J15:J17"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="C3:K3"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="C9:K9"/>
-    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C22:K22"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="J23:J25"/>
+    <mergeCell ref="K23:K25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="I27:I29"/>
+    <mergeCell ref="J27:J29"/>
+    <mergeCell ref="K27:K29"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
